--- a/frontend/kskcolle/public/data/erelijsten/zomer.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/zomer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/Website KSK Colle/_/erelijsten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/KSKColle/frontend/kskcolle/public/data/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{4A3C6C07-254E-4627-A668-7BEA0E692A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8C97ACE-39E5-45D1-9585-F00B43CD5A91}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{4A3C6C07-254E-4627-A668-7BEA0E692A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E43C864C-4F69-4BEE-9FD2-31792BB26F0D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Zomertornooi" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
   <si>
     <t>Jaar</t>
   </si>
@@ -697,7 +697,7 @@
       </c>
       <c r="H4" s="14">
         <f>COUNTIF($B$3:$E$28,"*Björn Dyckmans*")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1181,8 +1181,12 @@
         <v>19</v>
       </c>
       <c r="C28" s="11"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="1">
+        <v>2026</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="18"/>
